--- a/InputData/bldgs/MDSC/Max Distrib Solar Capacity.xlsx
+++ b/InputData/bldgs/MDSC/Max Distrib Solar Capacity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\PA\bldgs\MDSC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\state-eps-data\PA\bldgs\MDSC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{09805EF3-F9B3-402B-A564-3D572E72F92B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1EA9C47F-E23D-47D2-A011-7AFC0F3BE343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -1624,6 +1624,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="About"/>
@@ -1940,13 +1941,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G51"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="79.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="79.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1954,7 +1955,7 @@
         <v>210</v>
       </c>
       <c r="C1" s="31">
-        <v>45686</v>
+        <v>46185</v>
       </c>
       <c r="D1" s="32"/>
       <c r="E1" s="32"/>
@@ -1965,7 +1966,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" t="str">
         <f>LOOKUP(B1,F2:G51,G2:G51)</f>
         <v>PA</v>
@@ -1979,7 +1980,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1993,7 +1994,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>3</v>
       </c>
@@ -2004,7 +2005,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B5" s="3">
         <v>2016</v>
       </c>
@@ -2015,7 +2016,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>4</v>
       </c>
@@ -2026,7 +2027,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>5</v>
       </c>
@@ -2037,7 +2038,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>6</v>
       </c>
@@ -2048,7 +2049,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F9" s="30" t="s">
         <v>220</v>
       </c>
@@ -2056,7 +2057,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>169</v>
       </c>
@@ -2067,7 +2068,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>170</v>
       </c>
@@ -2078,7 +2079,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
         <v>2020</v>
       </c>
@@ -2089,7 +2090,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>171</v>
       </c>
@@ -2100,7 +2101,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
         <v>172</v>
       </c>
@@ -2111,7 +2112,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
         <v>173</v>
       </c>
@@ -2122,7 +2123,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>174</v>
       </c>
@@ -2133,7 +2134,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F17" s="30" t="s">
         <v>196</v>
       </c>
@@ -2141,7 +2142,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>7</v>
       </c>
@@ -2152,7 +2153,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>270</v>
       </c>
@@ -2163,7 +2164,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>177</v>
       </c>
@@ -2174,7 +2175,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F21" s="30" t="s">
         <v>200</v>
       </c>
@@ -2182,7 +2183,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>178</v>
       </c>
@@ -2193,7 +2194,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F23" s="30" t="s">
         <v>191</v>
       </c>
@@ -2201,7 +2202,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>175</v>
       </c>
@@ -2212,7 +2213,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>176</v>
       </c>
@@ -2223,7 +2224,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F26" s="30" t="s">
         <v>195</v>
       </c>
@@ -2231,7 +2232,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>244</v>
       </c>
@@ -2242,7 +2243,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>37</v>
       </c>
@@ -2257,7 +2258,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -2272,7 +2273,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F30" s="30" t="s">
         <v>187</v>
       </c>
@@ -2280,7 +2281,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F31" s="30" t="s">
         <v>198</v>
       </c>
@@ -2288,7 +2289,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F32" s="30" t="s">
         <v>194</v>
       </c>
@@ -2296,7 +2297,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="33" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="33" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F33" s="30" t="s">
         <v>203</v>
       </c>
@@ -2304,7 +2305,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="34" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="34" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F34" s="30" t="s">
         <v>208</v>
       </c>
@@ -2312,7 +2313,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="35" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="35" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F35" s="30" t="s">
         <v>229</v>
       </c>
@@ -2320,7 +2321,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="36" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="36" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F36" s="30" t="s">
         <v>205</v>
       </c>
@@ -2328,7 +2329,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="37" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="37" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F37" s="30" t="s">
         <v>193</v>
       </c>
@@ -2336,7 +2337,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="38" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="38" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F38" s="30" t="s">
         <v>213</v>
       </c>
@@ -2344,7 +2345,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="39" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="39" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F39" s="30" t="s">
         <v>210</v>
       </c>
@@ -2352,7 +2353,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="40" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="40" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F40" s="30" t="s">
         <v>186</v>
       </c>
@@ -2360,7 +2361,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="41" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="41" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F41" s="30" t="s">
         <v>228</v>
       </c>
@@ -2368,7 +2369,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="42" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="42" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F42" s="30" t="s">
         <v>202</v>
       </c>
@@ -2376,7 +2377,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="43" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="43" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F43" s="30" t="s">
         <v>218</v>
       </c>
@@ -2384,7 +2385,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="44" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="44" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F44" s="30" t="s">
         <v>207</v>
       </c>
@@ -2392,7 +2393,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="45" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="45" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F45" s="30" t="s">
         <v>212</v>
       </c>
@@ -2400,7 +2401,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="46" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="46" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F46" s="30" t="s">
         <v>185</v>
       </c>
@@ -2408,7 +2409,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="47" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="47" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F47" s="30" t="s">
         <v>217</v>
       </c>
@@ -2416,7 +2417,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="48" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="48" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F48" s="30" t="s">
         <v>225</v>
       </c>
@@ -2424,7 +2425,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="49" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="49" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F49" s="30" t="s">
         <v>230</v>
       </c>
@@ -2432,7 +2433,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="50" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="50" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F50" s="30" t="s">
         <v>199</v>
       </c>
@@ -2440,7 +2441,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="51" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="51" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F51" s="30" t="s">
         <v>232</v>
       </c>
@@ -2461,19 +2462,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93DBD78C-B2BD-4BF0-BA7A-1C9C74DD0B3E}">
   <dimension ref="A1:G222"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.7265625" customWidth="1"/>
-    <col min="2" max="7" width="11.7265625" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" customWidth="1"/>
+    <col min="2" max="7" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="34" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="34"/>
     </row>
-    <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="35" t="s">
         <v>9</v>
       </c>
@@ -2484,7 +2485,7 @@
       <c r="F2" s="36"/>
       <c r="G2" s="36"/>
     </row>
-    <row r="3" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="3" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="37" t="s">
         <v>10</v>
@@ -2495,7 +2496,7 @@
       <c r="F3" s="37"/>
       <c r="G3" s="38"/>
     </row>
-    <row r="4" spans="1:7" ht="23.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.8">
+    <row r="4" spans="1:7" ht="23.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
       <c r="B4" s="7"/>
       <c r="C4" s="39" t="s">
@@ -2506,7 +2507,7 @@
       <c r="F4" s="39"/>
       <c r="G4" s="39"/>
     </row>
-    <row r="5" spans="1:7" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="5" spans="1:7" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8"/>
       <c r="B5" s="9" t="s">
         <v>12</v>
@@ -2527,7 +2528,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="24" customHeight="1" thickTop="1" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:7" ht="24" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>18</v>
       </c>
@@ -2550,7 +2551,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>19</v>
       </c>
@@ -2573,7 +2574,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>21</v>
       </c>
@@ -2596,7 +2597,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>22</v>
       </c>
@@ -2619,7 +2620,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>23</v>
       </c>
@@ -2642,7 +2643,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>24</v>
       </c>
@@ -2665,7 +2666,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>25</v>
       </c>
@@ -2688,7 +2689,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>26</v>
       </c>
@@ -2711,7 +2712,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>27</v>
       </c>
@@ -2734,7 +2735,7 @@
         <v>3.89</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>28</v>
       </c>
@@ -2757,7 +2758,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>29</v>
       </c>
@@ -2780,7 +2781,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>30</v>
       </c>
@@ -2803,7 +2804,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>31</v>
       </c>
@@ -2826,7 +2827,7 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>32</v>
       </c>
@@ -2849,7 +2850,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>33</v>
       </c>
@@ -2872,7 +2873,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>34</v>
       </c>
@@ -2895,7 +2896,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
         <v>35</v>
       </c>
@@ -2918,7 +2919,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>36</v>
       </c>
@@ -2941,7 +2942,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>37</v>
       </c>
@@ -2964,7 +2965,7 @@
         <v>3.31</v>
       </c>
     </row>
-    <row r="25" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>38</v>
       </c>
@@ -2987,7 +2988,7 @@
         <v>2.5299999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
         <v>39</v>
       </c>
@@ -3010,7 +3011,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
         <v>40</v>
       </c>
@@ -3033,7 +3034,7 @@
         <v>3.52</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
         <v>41</v>
       </c>
@@ -3056,7 +3057,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
         <v>42</v>
       </c>
@@ -3079,7 +3080,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
         <v>43</v>
       </c>
@@ -3102,7 +3103,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
         <v>44</v>
       </c>
@@ -3125,7 +3126,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
         <v>45</v>
       </c>
@@ -3148,7 +3149,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
         <v>46</v>
       </c>
@@ -3171,7 +3172,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
         <v>47</v>
       </c>
@@ -3194,7 +3195,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
         <v>48</v>
       </c>
@@ -3217,7 +3218,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
         <v>49</v>
       </c>
@@ -3240,7 +3241,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
         <v>50</v>
       </c>
@@ -3263,7 +3264,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
         <v>51</v>
       </c>
@@ -3286,7 +3287,7 @@
         <v>1.34</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
         <v>52</v>
       </c>
@@ -3309,7 +3310,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
         <v>53</v>
       </c>
@@ -3332,7 +3333,7 @@
         <v>1.92</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>54</v>
       </c>
@@ -3355,7 +3356,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="14" t="s">
         <v>55</v>
       </c>
@@ -3378,7 +3379,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>56</v>
       </c>
@@ -3401,7 +3402,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
         <v>57</v>
       </c>
@@ -3424,7 +3425,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="s">
         <v>58</v>
       </c>
@@ -3447,7 +3448,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
         <v>60</v>
       </c>
@@ -3470,7 +3471,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="47" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="14" t="s">
         <v>61</v>
       </c>
@@ -3493,7 +3494,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
         <v>62</v>
       </c>
@@ -3516,7 +3517,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="s">
         <v>63</v>
       </c>
@@ -3539,7 +3540,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
         <v>64</v>
       </c>
@@ -3562,7 +3563,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A51" s="14" t="s">
         <v>65</v>
       </c>
@@ -3585,7 +3586,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
         <v>66</v>
       </c>
@@ -3608,7 +3609,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="53" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="14" t="s">
         <v>67</v>
       </c>
@@ -3631,7 +3632,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="54" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="14" t="s">
         <v>68</v>
       </c>
@@ -3654,7 +3655,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="14" t="s">
         <v>69</v>
       </c>
@@ -3677,7 +3678,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="14" t="s">
         <v>71</v>
       </c>
@@ -3700,7 +3701,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>72</v>
       </c>
@@ -3723,7 +3724,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="14" t="s">
         <v>73</v>
       </c>
@@ -3746,7 +3747,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
         <v>74</v>
       </c>
@@ -3769,7 +3770,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="14" t="s">
         <v>75</v>
       </c>
@@ -3792,7 +3793,7 @@
         <v>3.09</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="14" t="s">
         <v>76</v>
       </c>
@@ -3815,7 +3816,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="62" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="14" t="s">
         <v>77</v>
       </c>
@@ -3838,7 +3839,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="14" t="s">
         <v>78</v>
       </c>
@@ -3861,7 +3862,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="14" t="s">
         <v>79</v>
       </c>
@@ -3884,7 +3885,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="14" t="s">
         <v>80</v>
       </c>
@@ -3907,7 +3908,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="14" t="s">
         <v>73</v>
       </c>
@@ -3930,7 +3931,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
+    <row r="67" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A67" s="14" t="s">
         <v>81</v>
       </c>
@@ -3953,7 +3954,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
+    <row r="68" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
         <v>82</v>
       </c>
@@ -3976,7 +3977,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="19" t="s">
         <v>83</v>
       </c>
@@ -3999,7 +4000,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="19">
         <v>3</v>
       </c>
@@ -4022,7 +4023,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="71" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="19">
         <v>4</v>
       </c>
@@ -4045,7 +4046,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="19">
         <v>5</v>
       </c>
@@ -4068,7 +4069,7 @@
         <v>1.65</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="19">
         <v>6</v>
       </c>
@@ -4091,7 +4092,7 @@
         <v>1.94</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="19">
         <v>7</v>
       </c>
@@ -4114,7 +4115,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="19">
         <v>8</v>
       </c>
@@ -4137,7 +4138,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="19" t="s">
         <v>84</v>
       </c>
@@ -4160,7 +4161,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
         <v>85</v>
       </c>
@@ -4183,7 +4184,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="19">
         <v>0</v>
       </c>
@@ -4206,7 +4207,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="19">
         <v>1</v>
       </c>
@@ -4229,7 +4230,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="80" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="19">
         <v>2</v>
       </c>
@@ -4252,7 +4253,7 @@
         <v>2.36</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="19">
         <v>3</v>
       </c>
@@ -4275,7 +4276,7 @@
         <v>3.49</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="19">
         <v>4</v>
       </c>
@@ -4298,7 +4299,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="19" t="s">
         <v>86</v>
       </c>
@@ -4321,7 +4322,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
+    <row r="84" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
         <v>87</v>
       </c>
@@ -4344,7 +4345,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="19">
         <v>1</v>
       </c>
@@ -4367,7 +4368,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="19">
         <v>2</v>
       </c>
@@ -4390,7 +4391,7 @@
         <v>2.13</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="87" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="19">
         <v>3</v>
       </c>
@@ -4413,7 +4414,7 @@
         <v>2.36</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="19">
         <v>4</v>
       </c>
@@ -4436,7 +4437,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="19" t="s">
         <v>86</v>
       </c>
@@ -4459,7 +4460,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="12" t="s">
         <v>88</v>
       </c>
@@ -4482,7 +4483,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="19">
         <v>0</v>
       </c>
@@ -4505,7 +4506,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="19">
         <v>1</v>
       </c>
@@ -4528,7 +4529,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="93" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="19">
         <v>2</v>
       </c>
@@ -4551,7 +4552,7 @@
         <v>4.51</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="19" t="s">
         <v>89</v>
       </c>
@@ -4574,7 +4575,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
         <v>90</v>
       </c>
@@ -4597,7 +4598,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="19">
         <v>0</v>
       </c>
@@ -4620,7 +4621,7 @@
         <v>5.98</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="19">
         <v>1</v>
       </c>
@@ -4643,7 +4644,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="98" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="19" t="s">
         <v>91</v>
       </c>
@@ -4666,7 +4667,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="12" t="s">
         <v>92</v>
       </c>
@@ -4689,7 +4690,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="14" t="s">
         <v>93</v>
       </c>
@@ -4712,7 +4713,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="16" t="s">
         <v>94</v>
       </c>
@@ -4735,7 +4736,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="102" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="16" t="s">
         <v>95</v>
       </c>
@@ -4758,7 +4759,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="19" t="s">
         <v>96</v>
       </c>
@@ -4781,7 +4782,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
+    <row r="104" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A104" s="19" t="s">
         <v>63</v>
       </c>
@@ -4804,7 +4805,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="12" t="s">
         <v>97</v>
       </c>
@@ -4827,7 +4828,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="14" t="s">
         <v>93</v>
       </c>
@@ -4850,7 +4851,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="16" t="s">
         <v>98</v>
       </c>
@@ -4873,7 +4874,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="108" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="16" t="s">
         <v>99</v>
       </c>
@@ -4896,7 +4897,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="14" t="s">
         <v>96</v>
       </c>
@@ -4919,7 +4920,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
+    <row r="110" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A110" s="19" t="s">
         <v>63</v>
       </c>
@@ -4942,7 +4943,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="12" t="s">
         <v>100</v>
       </c>
@@ -4965,7 +4966,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="14" t="s">
         <v>93</v>
       </c>
@@ -4988,7 +4989,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="16" t="s">
         <v>101</v>
       </c>
@@ -5011,7 +5012,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="114" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="16" t="s">
         <v>102</v>
       </c>
@@ -5034,7 +5035,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="115" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="16" t="s">
         <v>103</v>
       </c>
@@ -5057,7 +5058,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="14" t="s">
         <v>96</v>
       </c>
@@ -5080,7 +5081,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
+    <row r="117" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A117" s="19" t="s">
         <v>63</v>
       </c>
@@ -5103,7 +5104,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="12" t="s">
         <v>104</v>
       </c>
@@ -5126,7 +5127,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="14" t="s">
         <v>105</v>
       </c>
@@ -5149,7 +5150,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="14" t="s">
         <v>106</v>
       </c>
@@ -5172,7 +5173,7 @@
         <v>3.28</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="121" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="14" t="s">
         <v>107</v>
       </c>
@@ -5195,7 +5196,7 @@
         <v>1.87</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="14" t="s">
         <v>108</v>
       </c>
@@ -5218,7 +5219,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
+    <row r="123" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A123" s="12" t="s">
         <v>109</v>
       </c>
@@ -5241,7 +5242,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="14" t="s">
         <v>110</v>
       </c>
@@ -5264,7 +5265,7 @@
         <v>2.41</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="14" t="s">
         <v>111</v>
       </c>
@@ -5287,7 +5288,7 @@
         <v>3.19</v>
       </c>
     </row>
-    <row r="126" spans="1:7" s="18" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="126" spans="1:7" s="18" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="14" t="s">
         <v>112</v>
       </c>
@@ -5310,7 +5311,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="127" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="127" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="14" t="s">
         <v>113</v>
       </c>
@@ -5333,7 +5334,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="128" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="128" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="12" t="s">
         <v>114</v>
       </c>
@@ -5356,7 +5357,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="14" t="s">
         <v>93</v>
       </c>
@@ -5379,7 +5380,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="14" t="s">
         <v>96</v>
       </c>
@@ -5402,7 +5403,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="131" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="19" t="s">
         <v>115</v>
       </c>
@@ -5425,7 +5426,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
         <v>116</v>
       </c>
@@ -5448,7 +5449,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="14" t="s">
         <v>117</v>
       </c>
@@ -5471,7 +5472,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="14" t="s">
         <v>118</v>
       </c>
@@ -5494,7 +5495,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="135" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="14" t="s">
         <v>119</v>
       </c>
@@ -5517,7 +5518,7 @@
         <v>2.66</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="20" t="s">
         <v>120</v>
       </c>
@@ -5540,7 +5541,7 @@
         <v>3.23</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="20" t="s">
         <v>121</v>
       </c>
@@ -5563,7 +5564,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="20" t="s">
         <v>122</v>
       </c>
@@ -5586,7 +5587,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="20" t="s">
         <v>123</v>
       </c>
@@ -5609,7 +5610,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="12" t="s">
         <v>124</v>
       </c>
@@ -5632,7 +5633,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="14" t="s">
         <v>125</v>
       </c>
@@ -5655,7 +5656,7 @@
         <v>3.46</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="14" t="s">
         <v>126</v>
       </c>
@@ -5678,7 +5679,7 @@
         <v>3.29</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="143" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="14" t="s">
         <v>127</v>
       </c>
@@ -5701,7 +5702,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="12" t="s">
         <v>128</v>
       </c>
@@ -5724,7 +5725,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="14" t="s">
         <v>129</v>
       </c>
@@ -5747,7 +5748,7 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="14" t="s">
         <v>67</v>
       </c>
@@ -5770,7 +5771,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="147" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="14" t="s">
         <v>130</v>
       </c>
@@ -5793,7 +5794,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="20" t="s">
         <v>131</v>
       </c>
@@ -5816,7 +5817,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="20" t="s">
         <v>132</v>
       </c>
@@ -5839,7 +5840,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
+    <row r="150" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A150" s="12" t="s">
         <v>133</v>
       </c>
@@ -5862,7 +5863,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="19">
         <v>0</v>
       </c>
@@ -5885,7 +5886,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="19">
         <v>1</v>
       </c>
@@ -5908,7 +5909,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="153" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="19">
         <v>2</v>
       </c>
@@ -5931,7 +5932,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="19" t="s">
         <v>89</v>
       </c>
@@ -5954,7 +5955,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="12" t="s">
         <v>134</v>
       </c>
@@ -5977,7 +5978,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="14" t="s">
         <v>93</v>
       </c>
@@ -6000,7 +6001,7 @@
         <v>1.82</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="14" t="s">
         <v>96</v>
       </c>
@@ -6023,7 +6024,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="158" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="158" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="14" t="s">
         <v>135</v>
       </c>
@@ -6046,7 +6047,7 @@
         <v>2.66</v>
       </c>
     </row>
-    <row r="159" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
+    <row r="159" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A159" s="12" t="s">
         <v>136</v>
       </c>
@@ -6069,7 +6070,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="14" t="s">
         <v>93</v>
       </c>
@@ -6092,7 +6093,7 @@
         <v>3.41</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="14" t="s">
         <v>96</v>
       </c>
@@ -6115,7 +6116,7 @@
         <v>3.42</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="162" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="14" t="s">
         <v>81</v>
       </c>
@@ -6138,7 +6139,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="163" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
+    <row r="163" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A163" s="12" t="s">
         <v>137</v>
       </c>
@@ -6161,7 +6162,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="14" t="s">
         <v>93</v>
       </c>
@@ -6184,7 +6185,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="16" t="s">
         <v>138</v>
       </c>
@@ -6207,7 +6208,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="166" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="166" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="14" t="s">
         <v>96</v>
       </c>
@@ -6230,7 +6231,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
+    <row r="167" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A167" s="12" t="s">
         <v>139</v>
       </c>
@@ -6253,7 +6254,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" s="14" t="s">
         <v>93</v>
       </c>
@@ -6276,7 +6277,7 @@
         <v>2.87</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="16" t="s">
         <v>140</v>
       </c>
@@ -6299,7 +6300,7 @@
         <v>1.89</v>
       </c>
     </row>
-    <row r="170" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="170" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="16" t="s">
         <v>141</v>
       </c>
@@ -6322,7 +6323,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="14" t="s">
         <v>96</v>
       </c>
@@ -6345,7 +6346,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="12" t="s">
         <v>142</v>
       </c>
@@ -6368,7 +6369,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="14" t="s">
         <v>93</v>
       </c>
@@ -6391,7 +6392,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="14" t="s">
         <v>96</v>
       </c>
@@ -6414,7 +6415,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="175" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="175" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="14" t="s">
         <v>143</v>
       </c>
@@ -6437,7 +6438,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
+    <row r="176" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A176" s="12" t="s">
         <v>144</v>
       </c>
@@ -6460,7 +6461,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="14" t="s">
         <v>93</v>
       </c>
@@ -6483,7 +6484,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
+    <row r="178" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A178" s="16" t="s">
         <v>145</v>
       </c>
@@ -6506,7 +6507,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="179" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="179" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="16" t="s">
         <v>146</v>
       </c>
@@ -6529,7 +6530,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="180" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
+    <row r="180" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A180" s="16" t="s">
         <v>147</v>
       </c>
@@ -6552,7 +6553,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" s="16" t="s">
         <v>148</v>
       </c>
@@ -6575,7 +6576,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="14" t="s">
         <v>96</v>
       </c>
@@ -6598,7 +6599,7 @@
         <v>5.33</v>
       </c>
     </row>
-    <row r="183" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="183" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="12" t="s">
         <v>149</v>
       </c>
@@ -6621,7 +6622,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="14" t="s">
         <v>93</v>
       </c>
@@ -6644,7 +6645,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="14" t="s">
         <v>96</v>
       </c>
@@ -6667,7 +6668,7 @@
         <v>5.82</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="12" t="s">
         <v>150</v>
       </c>
@@ -6690,7 +6691,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="187" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="187" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="19" t="s">
         <v>93</v>
       </c>
@@ -6713,7 +6714,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="14" t="s">
         <v>96</v>
       </c>
@@ -6736,7 +6737,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="14" t="s">
         <v>143</v>
       </c>
@@ -6759,7 +6760,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="22" t="s">
         <v>151</v>
       </c>
@@ -6782,7 +6783,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="16" t="s">
         <v>152</v>
       </c>
@@ -6805,7 +6806,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" s="16" t="s">
         <v>153</v>
       </c>
@@ -6828,7 +6829,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="193" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="193" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="16" t="s">
         <v>154</v>
       </c>
@@ -6851,7 +6852,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="16" t="s">
         <v>155</v>
       </c>
@@ -6874,7 +6875,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="16" t="s">
         <v>143</v>
       </c>
@@ -6897,7 +6898,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="22" t="s">
         <v>156</v>
       </c>
@@ -6920,7 +6921,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="16" t="s">
         <v>157</v>
       </c>
@@ -6943,7 +6944,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="17" t="s">
         <v>158</v>
       </c>
@@ -6966,7 +6967,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="17" t="s">
         <v>159</v>
       </c>
@@ -6989,7 +6990,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="17" t="s">
         <v>160</v>
       </c>
@@ -7012,7 +7013,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="17" t="s">
         <v>161</v>
       </c>
@@ -7035,7 +7036,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="16" t="s">
         <v>162</v>
       </c>
@@ -7058,7 +7059,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="203" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="203" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="16" t="s">
         <v>155</v>
       </c>
@@ -7081,7 +7082,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="204" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="204" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A204" s="16" t="s">
         <v>143</v>
       </c>
@@ -7104,7 +7105,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="205" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="205" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="12" t="s">
         <v>163</v>
       </c>
@@ -7127,7 +7128,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="206" spans="1:7" s="18" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="206" spans="1:7" s="18" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="14" t="s">
         <v>93</v>
       </c>
@@ -7150,7 +7151,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="207" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="207" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A207" s="14" t="s">
         <v>96</v>
       </c>
@@ -7173,7 +7174,7 @@
         <v>6.55</v>
       </c>
     </row>
-    <row r="208" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="208" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="22" t="s">
         <v>164</v>
       </c>
@@ -7196,7 +7197,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="209" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="209" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="16" t="s">
         <v>152</v>
       </c>
@@ -7219,7 +7220,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="210" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="210" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="16" t="s">
         <v>153</v>
       </c>
@@ -7242,7 +7243,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="211" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="211" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="16" t="s">
         <v>154</v>
       </c>
@@ -7265,7 +7266,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" s="16" t="s">
         <v>165</v>
       </c>
@@ -7288,7 +7289,7 @@
         <v>6.55</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" s="22" t="s">
         <v>166</v>
       </c>
@@ -7311,7 +7312,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" s="16" t="s">
         <v>158</v>
       </c>
@@ -7334,7 +7335,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" s="16" t="s">
         <v>159</v>
       </c>
@@ -7357,7 +7358,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" s="16" t="s">
         <v>161</v>
       </c>
@@ -7380,7 +7381,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="217" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="217" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="16" t="s">
         <v>167</v>
       </c>
@@ -7403,7 +7404,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" s="16" t="s">
         <v>165</v>
       </c>
@@ -7426,7 +7427,7 @@
         <v>6.55</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" s="14"/>
       <c r="B219" s="23"/>
       <c r="C219" s="23"/>
@@ -7435,7 +7436,7 @@
       <c r="F219" s="23"/>
       <c r="G219" s="23"/>
     </row>
-    <row r="220" spans="1:7" s="18" customFormat="1" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="220" spans="1:7" s="18" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="16"/>
       <c r="B220" s="15"/>
       <c r="C220" s="15"/>
@@ -7444,7 +7445,7 @@
       <c r="F220" s="15"/>
       <c r="G220" s="15"/>
     </row>
-    <row r="221" spans="1:7" s="18" customFormat="1" ht="206.25" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="221" spans="1:7" s="18" customFormat="1" ht="206.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="40" t="s">
         <v>168</v>
       </c>
@@ -7455,7 +7456,7 @@
       <c r="F221" s="40"/>
       <c r="G221" s="40"/>
     </row>
-    <row r="222" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="222" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A222"/>
       <c r="B222"/>
       <c r="C222"/>
@@ -7479,18 +7480,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F9A8513-7C6F-4F9E-85C5-0991DA7B58D4}">
   <dimension ref="B2:F53"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="19.40625" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="27.1328125" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="3" spans="2:6" ht="31.5" x14ac:dyDescent="0.75">
+    <row r="3" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>180</v>
       </c>
@@ -7507,7 +7508,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>183</v>
       </c>
@@ -7524,7 +7525,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>184</v>
       </c>
@@ -7541,7 +7542,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>185</v>
       </c>
@@ -7558,7 +7559,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>186</v>
       </c>
@@ -7575,7 +7576,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>187</v>
       </c>
@@ -7592,7 +7593,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>188</v>
       </c>
@@ -7609,7 +7610,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>189</v>
       </c>
@@ -7626,7 +7627,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>190</v>
       </c>
@@ -7643,7 +7644,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>191</v>
       </c>
@@ -7660,7 +7661,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>192</v>
       </c>
@@ -7677,7 +7678,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>193</v>
       </c>
@@ -7694,7 +7695,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>194</v>
       </c>
@@ -7711,7 +7712,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>195</v>
       </c>
@@ -7728,7 +7729,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>196</v>
       </c>
@@ -7745,7 +7746,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>197</v>
       </c>
@@ -7762,7 +7763,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>198</v>
       </c>
@@ -7779,7 +7780,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>199</v>
       </c>
@@ -7796,7 +7797,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>200</v>
       </c>
@@ -7813,7 +7814,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>201</v>
       </c>
@@ -7830,7 +7831,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>202</v>
       </c>
@@ -7847,7 +7848,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>203</v>
       </c>
@@ -7864,7 +7865,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>204</v>
       </c>
@@ -7881,7 +7882,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>205</v>
       </c>
@@ -7898,7 +7899,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>206</v>
       </c>
@@ -7915,7 +7916,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>207</v>
       </c>
@@ -7932,7 +7933,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>208</v>
       </c>
@@ -7949,7 +7950,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>210</v>
       </c>
@@ -7966,7 +7967,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>211</v>
       </c>
@@ -7983,7 +7984,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>212</v>
       </c>
@@ -8000,7 +8001,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>213</v>
       </c>
@@ -8017,7 +8018,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>214</v>
       </c>
@@ -8034,7 +8035,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>215</v>
       </c>
@@ -8051,7 +8052,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>216</v>
       </c>
@@ -8068,7 +8069,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>217</v>
       </c>
@@ -8085,7 +8086,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>218</v>
       </c>
@@ -8102,7 +8103,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>219</v>
       </c>
@@ -8119,7 +8120,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>220</v>
       </c>
@@ -8136,7 +8137,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>221</v>
       </c>
@@ -8153,7 +8154,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>222</v>
       </c>
@@ -8170,7 +8171,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>223</v>
       </c>
@@ -8187,7 +8188,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>224</v>
       </c>
@@ -8204,7 +8205,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>225</v>
       </c>
@@ -8221,7 +8222,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>226</v>
       </c>
@@ -8238,7 +8239,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>227</v>
       </c>
@@ -8255,7 +8256,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>228</v>
       </c>
@@ -8272,7 +8273,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>229</v>
       </c>
@@ -8289,7 +8290,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>230</v>
       </c>
@@ -8306,7 +8307,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>231</v>
       </c>
@@ -8323,7 +8324,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>232</v>
       </c>
@@ -8340,7 +8341,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>233</v>
       </c>
@@ -8365,18 +8366,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{953422B1-328A-43F6-A21B-CBDD7BE13E26}">
   <dimension ref="B2:F53"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="19.40625" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="27.1328125" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="3" spans="2:6" s="5" customFormat="1" ht="31.5" x14ac:dyDescent="0.75">
+    <row r="3" spans="2:6" s="5" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>180</v>
       </c>
@@ -8393,7 +8394,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>237</v>
       </c>
@@ -8410,7 +8411,7 @@
         <v>525.5</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>185</v>
       </c>
@@ -8427,7 +8428,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>184</v>
       </c>
@@ -8444,7 +8445,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>194</v>
       </c>
@@ -8461,7 +8462,7 @@
         <v>32.6</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>187</v>
       </c>
@@ -8478,7 +8479,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>215</v>
       </c>
@@ -8495,7 +8496,7 @@
         <v>103.1</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>186</v>
       </c>
@@ -8512,7 +8513,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>191</v>
       </c>
@@ -8529,7 +8530,7 @@
         <v>189.2</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>190</v>
       </c>
@@ -8546,7 +8547,7 @@
         <v>343.4</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>202</v>
       </c>
@@ -8563,7 +8564,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>195</v>
       </c>
@@ -8580,7 +8581,7 @@
         <v>126.3</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>188</v>
       </c>
@@ -8597,7 +8598,7 @@
         <v>48.2</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>199</v>
       </c>
@@ -8614,7 +8615,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>193</v>
       </c>
@@ -8631,7 +8632,7 @@
         <v>80.900000000000006</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>196</v>
       </c>
@@ -8648,7 +8649,7 @@
         <v>55.3</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>192</v>
       </c>
@@ -8665,7 +8666,7 @@
         <v>67.400000000000006</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>224</v>
       </c>
@@ -8682,7 +8683,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>189</v>
       </c>
@@ -8699,7 +8700,7 @@
         <v>82.8</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>212</v>
       </c>
@@ -8716,7 +8717,7 @@
         <v>36.200000000000003</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>198</v>
       </c>
@@ -8733,7 +8734,7 @@
         <v>104.6</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>206</v>
       </c>
@@ -8750,7 +8751,7 @@
         <v>65.8</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>203</v>
       </c>
@@ -8767,7 +8768,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>204</v>
       </c>
@@ -8784,7 +8785,7 @@
         <v>192.4</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>208</v>
       </c>
@@ -8801,7 +8802,7 @@
         <v>160.1</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>213</v>
       </c>
@@ -8818,7 +8819,7 @@
         <v>65.3</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>210</v>
       </c>
@@ -8835,7 +8836,7 @@
         <v>198.8</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>205</v>
       </c>
@@ -8852,7 +8853,7 @@
         <v>206.5</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>201</v>
       </c>
@@ -8869,7 +8870,7 @@
         <v>92.7</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>216</v>
       </c>
@@ -8886,7 +8887,7 @@
         <v>55.7</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>226</v>
       </c>
@@ -8903,7 +8904,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>220</v>
       </c>
@@ -8920,7 +8921,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>207</v>
       </c>
@@ -8937,7 +8938,7 @@
         <v>424.6</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>218</v>
       </c>
@@ -8954,7 +8955,7 @@
         <v>114.6</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>197</v>
       </c>
@@ -8971,7 +8972,7 @@
         <v>32.9</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>214</v>
       </c>
@@ -8988,7 +8989,7 @@
         <v>149.6</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>200</v>
       </c>
@@ -9005,7 +9006,7 @@
         <v>72.099999999999994</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>217</v>
       </c>
@@ -9022,7 +9023,7 @@
         <v>121.6</v>
       </c>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>219</v>
       </c>
@@ -9039,7 +9040,7 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>223</v>
       </c>
@@ -9056,7 +9057,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>211</v>
       </c>
@@ -9073,7 +9074,7 @@
         <v>32.1</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>222</v>
       </c>
@@ -9090,7 +9091,7 @@
         <v>88.1</v>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>228</v>
       </c>
@@ -9107,7 +9108,7 @@
         <v>76.2</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>221</v>
       </c>
@@ -9124,7 +9125,7 @@
         <v>83.5</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>229</v>
       </c>
@@ -9141,7 +9142,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>225</v>
       </c>
@@ -9158,7 +9159,7 @@
         <v>105.6</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>230</v>
       </c>
@@ -9175,7 +9176,7 @@
         <v>32.299999999999997</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>227</v>
       </c>
@@ -9192,7 +9193,7 @@
         <v>77.599999999999994</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>232</v>
       </c>
@@ -9209,7 +9210,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>238</v>
       </c>
@@ -9226,7 +9227,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.75">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>233</v>
       </c>
@@ -9251,18 +9252,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3CE1901-2698-4C54-802E-51343240533F}">
   <dimension ref="A2:F53"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="19.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="27.1328125" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="5" customFormat="1" ht="31.5" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:6" s="5" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>180</v>
       </c>
@@ -9279,7 +9280,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>INDEX(About!G:G,MATCH(B4,About!F:F,0))</f>
         <v>CA</v>
@@ -9300,7 +9301,7 @@
         <v>435.3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>INDEX(About!G:G,MATCH(B5,About!F:F,0))</f>
         <v>RI</v>
@@ -9321,7 +9322,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>INDEX(About!G:G,MATCH(B6,About!F:F,0))</f>
         <v>CT</v>
@@ -9342,7 +9343,7 @@
         <v>46.3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>INDEX(About!G:G,MATCH(B7,About!F:F,0))</f>
         <v>MA</v>
@@ -9363,7 +9364,7 @@
         <v>82.4</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>INDEX(About!G:G,MATCH(B8,About!F:F,0))</f>
         <v>NH</v>
@@ -9384,7 +9385,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>INDEX(About!G:G,MATCH(B9,About!F:F,0))</f>
         <v>ME</v>
@@ -9405,7 +9406,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>INDEX(About!G:G,MATCH(B10,About!F:F,0))</f>
         <v>VT</v>
@@ -9426,7 +9427,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>INDEX(About!G:G,MATCH(B11,About!F:F,0))</f>
         <v>NV</v>
@@ -9447,7 +9448,7 @@
         <v>33.799999999999997</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>INDEX(About!G:G,MATCH(B12,About!F:F,0))</f>
         <v>MD</v>
@@ -9468,7 +9469,7 @@
         <v>70.400000000000006</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>INDEX(About!G:G,MATCH(B13,About!F:F,0))</f>
         <v>CO</v>
@@ -9489,7 +9490,7 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>INDEX(About!G:G,MATCH(B14,About!F:F,0))</f>
         <v>OK</v>
@@ -9510,7 +9511,7 @@
         <v>59.5</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>INDEX(About!G:G,MATCH(B15,About!F:F,0))</f>
         <v>FL</v>
@@ -9531,7 +9532,7 @@
         <v>213.6</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>INDEX(About!G:G,MATCH(B16,About!F:F,0))</f>
         <v>NJ</v>
@@ -9552,7 +9553,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>INDEX(About!G:G,MATCH(B17,About!F:F,0))</f>
         <v>MN</v>
@@ -9573,7 +9574,7 @@
         <v>75.7</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>INDEX(About!G:G,MATCH(B18,About!F:F,0))</f>
         <v>MI</v>
@@ -9594,7 +9595,7 @@
         <v>114.1</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>INDEX(About!G:G,MATCH(B19,About!F:F,0))</f>
         <v>MO</v>
@@ -9615,7 +9616,7 @@
         <v>78.099999999999994</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>INDEX(About!G:G,MATCH(B20,About!F:F,0))</f>
         <v>KS</v>
@@ -9636,7 +9637,7 @@
         <v>34.700000000000003</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>INDEX(About!G:G,MATCH(B21,About!F:F,0))</f>
         <v>NE</v>
@@ -9657,7 +9658,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>INDEX(About!G:G,MATCH(B22,About!F:F,0))</f>
         <v>IL</v>
@@ -9678,7 +9679,7 @@
         <v>131.6</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>INDEX(About!G:G,MATCH(B23,About!F:F,0))</f>
         <v>TX</v>
@@ -9699,7 +9700,7 @@
         <v>289.89999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>INDEX(About!G:G,MATCH(B24,About!F:F,0))</f>
         <v>NY</v>
@@ -9720,7 +9721,7 @@
         <v>129.69999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>INDEX(About!G:G,MATCH(B25,About!F:F,0))</f>
         <v>WI</v>
@@ -9741,7 +9742,7 @@
         <v>60.2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>INDEX(About!G:G,MATCH(B26,About!F:F,0))</f>
         <v>OH</v>
@@ -9762,7 +9763,7 @@
         <v>131.30000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>INDEX(About!G:G,MATCH(B27,About!F:F,0))</f>
         <v>GA</v>
@@ -9783,7 +9784,7 @@
         <v>101.9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>INDEX(About!G:G,MATCH(B28,About!F:F,0))</f>
         <v>VA</v>
@@ -9804,7 +9805,7 @@
         <v>83.9</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>INDEX(About!G:G,MATCH(B29,About!F:F,0))</f>
         <v>LA</v>
@@ -9825,7 +9826,7 @@
         <v>62.6</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>INDEX(About!G:G,MATCH(B30,About!F:F,0))</f>
         <v>NC</v>
@@ -9846,7 +9847,7 @@
         <v>92.3</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>INDEX(About!G:G,MATCH(B31,About!F:F,0))</f>
         <v>PA</v>
@@ -9867,7 +9868,7 @@
         <v>116.8</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="e">
         <f>INDEX(About!G:G,MATCH(B32,About!F:F,0))</f>
         <v>#N/A</v>
@@ -9888,7 +9889,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>INDEX(About!G:G,MATCH(B33,About!F:F,0))</f>
         <v>OR</v>
@@ -9909,7 +9910,7 @@
         <v>35.6</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f>INDEX(About!G:G,MATCH(B34,About!F:F,0))</f>
         <v>AR</v>
@@ -9930,7 +9931,7 @@
         <v>31.9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
         <f>INDEX(About!G:G,MATCH(B35,About!F:F,0))</f>
         <v>AL</v>
@@ -9951,7 +9952,7 @@
         <v>58.6</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
         <f>INDEX(About!G:G,MATCH(B36,About!F:F,0))</f>
         <v>IA</v>
@@ -9972,7 +9973,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
         <f>INDEX(About!G:G,MATCH(B37,About!F:F,0))</f>
         <v>MS</v>
@@ -9993,7 +9994,7 @@
         <v>31.8</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
         <f>INDEX(About!G:G,MATCH(B38,About!F:F,0))</f>
         <v>NM</v>
@@ -10014,7 +10015,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
         <f>INDEX(About!G:G,MATCH(B39,About!F:F,0))</f>
         <v>TN</v>
@@ -10035,7 +10036,7 @@
         <v>60.4</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="str">
         <f>INDEX(About!G:G,MATCH(B40,About!F:F,0))</f>
         <v>SD</v>
@@ -10056,7 +10057,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="str">
         <f>INDEX(About!G:G,MATCH(B41,About!F:F,0))</f>
         <v>KY</v>
@@ -10077,7 +10078,7 @@
         <v>52.9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="str">
         <f>INDEX(About!G:G,MATCH(B42,About!F:F,0))</f>
         <v>IN</v>
@@ -10098,7 +10099,7 @@
         <v>65.900000000000006</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="str">
         <f>INDEX(About!G:G,MATCH(B43,About!F:F,0))</f>
         <v>UT</v>
@@ -10119,7 +10120,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="str">
         <f>INDEX(About!G:G,MATCH(B44,About!F:F,0))</f>
         <v>DE</v>
@@ -10140,7 +10141,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
         <f>INDEX(About!G:G,MATCH(B45,About!F:F,0))</f>
         <v>WA</v>
@@ -10161,7 +10162,7 @@
         <v>57.9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
         <f>INDEX(About!G:G,MATCH(B46,About!F:F,0))</f>
         <v>SC</v>
@@ -10182,7 +10183,7 @@
         <v>31.4</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
         <f>INDEX(About!G:G,MATCH(B47,About!F:F,0))</f>
         <v>ND</v>
@@ -10203,7 +10204,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="str">
         <f>INDEX(About!G:G,MATCH(B48,About!F:F,0))</f>
         <v>WV</v>
@@ -10224,7 +10225,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="str">
         <f>INDEX(About!G:G,MATCH(B49,About!F:F,0))</f>
         <v>ID</v>
@@ -10245,7 +10246,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="str">
         <f>INDEX(About!G:G,MATCH(B50,About!F:F,0))</f>
         <v>AZ</v>
@@ -10266,7 +10267,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="str">
         <f>INDEX(About!G:G,MATCH(B51,About!F:F,0))</f>
         <v>WY</v>
@@ -10287,7 +10288,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="str">
         <f>INDEX(About!G:G,MATCH(B52,About!F:F,0))</f>
         <v>MT</v>
@@ -10308,7 +10309,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="e">
         <f>INDEX(About!G:G,MATCH(B53,About!F:F,0))</f>
         <v>#N/A</v>
@@ -10340,15 +10341,15 @@
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>245</v>
       </c>
@@ -10362,7 +10363,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>246</v>
       </c>
@@ -10376,7 +10377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>247</v>
       </c>
@@ -10390,7 +10391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>248</v>
       </c>
@@ -10404,7 +10405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>249</v>
       </c>
@@ -10418,7 +10419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>250</v>
       </c>
@@ -10432,7 +10433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>251</v>
       </c>
@@ -10446,7 +10447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>252</v>
       </c>
@@ -10463,7 +10464,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>253</v>
       </c>
@@ -10477,7 +10478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>254</v>
       </c>
@@ -10491,7 +10492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>255</v>
       </c>
@@ -10505,7 +10506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>256</v>
       </c>
@@ -10519,7 +10520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>257</v>
       </c>
@@ -10533,7 +10534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>258</v>
       </c>
@@ -10547,7 +10548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>259</v>
       </c>
@@ -10561,7 +10562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>260</v>
       </c>
@@ -10575,7 +10576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>261</v>
       </c>
@@ -10589,7 +10590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>262</v>
       </c>
@@ -10603,7 +10604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>263</v>
       </c>
@@ -10617,7 +10618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>264</v>
       </c>
@@ -10631,7 +10632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>265</v>
       </c>
@@ -10645,7 +10646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>266</v>
       </c>
@@ -10659,7 +10660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>267</v>
       </c>
@@ -10673,7 +10674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>268</v>
       </c>
@@ -10687,7 +10688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>269</v>
       </c>
